--- a/assets/constructions/examples/ctd_tsmb_face_fullround.xlsx
+++ b/assets/constructions/examples/ctd_tsmb_face_fullround.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN6"/>
+  <dimension ref="A1:AS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,11 +629,36 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M662FGR050L15RCVTX</t>
+          <t>M662FGR100L15LCVTX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -678,7 +703,7 @@
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>5.55</v>
+        <v>5.45</v>
       </c>
       <c r="P2" t="n">
         <v>2.8</v>
@@ -693,17 +718,17 @@
         <v>42</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -755,21 +780,40 @@
           <t>2021/Groovex VARGUS</t>
         </is>
       </c>
+      <c r="AO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AR2" t="n">
+        <v>4955.23</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R610.1608-10/AL41F</t>
+          <t>M662FGR080L15RCVTX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DUEMMEL</t>
+          <t>VARGUS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ULTRAMINI</t>
+          <t>Microscope</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -777,17 +821,21 @@
           <t>PMKNS</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I3" t="n">
         <v>6</v>
       </c>
-      <c r="I3" t="n">
-        <v>4.9</v>
-      </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
@@ -800,23 +848,25 @@
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
+        <v>5.45</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="Q3" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="R3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="S3" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="T3" t="n">
         <v>1.6</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
         <v>0.8</v>
@@ -827,13 +877,15 @@
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
+      <c r="Y3" t="n">
+        <v>18.3</v>
+      </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>DUEM_DCON:6</t>
+          <t>VARGUS_D:6</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -843,12 +895,12 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>AL41F</t>
+          <t>VTX</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>TiALN</t>
+          <t>AlTiN</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
@@ -859,10 +911,10 @@
       </c>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
@@ -870,14 +922,33 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2019 / Duemmel Catalog</t>
+          <t>2021/Groovex VARGUS</t>
+        </is>
+      </c>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AR3" t="n">
+        <v>4955.23</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M662FGR125L15RCVTX</t>
+          <t>M662FGR150L15RCVTX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -937,13 +1008,13 @@
         <v>42</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -999,11 +1070,30 @@
           <t>2021/Groovex VARGUS</t>
         </is>
       </c>
+      <c r="AO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AR4" t="n">
+        <v>4955.23</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M662FGR080L15LCVTX</t>
+          <t>M662FGR100L15RCVTX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1063,17 +1153,17 @@
         <v>42</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -1125,43 +1215,62 @@
           <t>2021/Groovex VARGUS</t>
         </is>
       </c>
+      <c r="AO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AR5" t="n">
+        <v>4955.23</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M662FGR100L15LCVTX</t>
+          <t>R610.1005-10/NEME</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>DUEMMEL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Microscope</t>
+          <t>ULTRAMINI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PMKNS</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>O</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J6" t="n">
         <v>6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6.2</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
@@ -1174,44 +1283,40 @@
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.8</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="R6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="S6" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
         <v>2</v>
       </c>
-      <c r="U6" t="n">
-        <v>4</v>
-      </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="n">
-        <v>18.3</v>
-      </c>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>VARGUS_D:6</t>
+          <t>DUEM_DCON:6</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1221,12 +1326,12 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>VTX</t>
+          <t>NEME</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>AlTiN</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr"/>
@@ -1237,10 +1342,10 @@
       </c>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="n">
@@ -1248,7 +1353,26 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2021/Groovex VARGUS</t>
+          <t>2019 / Duemmel Catalog</t>
+        </is>
+      </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>75.52</v>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AR6" t="n">
+        <v>6942.83</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
